--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="22.77734375" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,21 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30-01-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Resr</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
